--- a/Översikt VARBERG.xlsx
+++ b/Översikt VARBERG.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45688</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46188</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>44834</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44834</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44768</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>45734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>46281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>46281</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>44918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45352</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45680</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44860</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45840</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>45744</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>45713</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45908</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>45343</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45141</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>44657</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45181</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44469</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>46174</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>46188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>45722</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45198</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46281</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>45434</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44831</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44655</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45300</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45324</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44635</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44722</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>44615</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44473</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>44575</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44509</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44862</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>44504</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>44581</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>44868</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44834</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>44466</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>44691</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>44641</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44797</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>44657</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>44588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>44876</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44876</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44638</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>44466</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>44699</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>44834</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44886</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44874</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44684</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44588</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44596</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44684</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44811</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44980</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44902</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44970</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>45271</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>45097</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>45054</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45642</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>45097</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>45259</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>44774</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>45341</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>45313</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>45737</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>45300</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>45609</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>45741</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>45583</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>44740</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>45743</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>45672</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>45336</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>45455</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>44896</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>44875</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>45749</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>44649</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>45561</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>45487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>44894</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>45769</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>44649</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>44935</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>44981</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>45182</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>45469</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>45323</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>45310</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>45600</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>45401</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45600</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45411</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45007</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>44974</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45058</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45736</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>44574</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44980</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>44649</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>44886</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45665</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45315</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45208</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>44711</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45623</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45884</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45582</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>45905</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45554</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45085</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>45159</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45477</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45932</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>45845</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45888</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45275</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45085</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45580</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45742</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45574</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45364</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45364</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45851</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>45897</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44622</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45884</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>45905</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45852</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>45910</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>45909</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>45908</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>45785</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>45929</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>45911</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>44827</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45392</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44837</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45743</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45792</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45912</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>45436</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>45635</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>45222</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>45695</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>45589</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>45925</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>44867</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45929</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45075</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45055</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>45929</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45932</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>45932</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45246</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>45436</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45328</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>44749</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>45938</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45279</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>44615</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45587</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45758</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45090</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>45945</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>45945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>45945</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44511</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>45401</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>45400</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>45952</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>45224</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44896</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45300</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45513</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>44935</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>44659</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>45954</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45261</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>44620</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44595</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45960</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45960</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45960</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44967</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>44904</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44641</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44470</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45246</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>45246</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45246</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>45359</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>45971</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>45973</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45593</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>44811</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>45734</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>45717</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45979</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45881</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45978</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45978</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>45302</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45980</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45705</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45985</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>45985</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45986</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>45404</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44797</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45988</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>46161</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>46161</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>44910</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44644</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44649</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45932</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>46161</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>45722</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45740</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>45994</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>45994</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>45994</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>45638</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44628</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>46164</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>45722</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>46164</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>44981</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45366</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>46003</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44652</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>46003</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>44657</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>46007</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>46007</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>45075</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>46007</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>46007</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>45678</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>46008</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45359</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>44470</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>46168</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>46010</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45574</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>46014</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>46014</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>46014</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>46014</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>46014</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>46008</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45197</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45590</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45580</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45701</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44533</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>44659</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>46024</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45281</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45210</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44851</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>46174</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45349</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>46174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45582</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45411</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45238</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45600</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>46047</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>46047</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>45509</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45372</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45369</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>46175</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>46175</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>46055</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44734</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>45302</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>46055</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45224</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45155</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>46064</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>46182</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45140</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45140</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45058</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45434</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>46188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>45196</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>46188</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45197</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>45706</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45762</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>46188</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45397</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>46092</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>45772</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45700</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>46190</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45722</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>46094</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>46094</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>46190</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>44770</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44985</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46196</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>46104</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45422</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>46196</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>46196</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>46106</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>44890</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>45090</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45246</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45140</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>46106</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45014</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>46202</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45567</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45344</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46120</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45716</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>46202</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45770</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>45708</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45579</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>46141</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45457</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>46199</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45744</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46132</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45487</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>46198</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44855</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>44981</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45104</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44722</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>46204</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>45272</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45743</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>45743</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45531</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45058</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>46210</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>45184</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>46251</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>45013</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>46251</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>46210</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29450,7 +29450,7 @@
         <v>46210</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>46210</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>45177</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44607</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>46255</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>46254</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>46255</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>45915</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45722</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>45722</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>45432</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45096</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45706</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>45706</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45361</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45086</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>45607</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>45754</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>45637</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45131</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>45762</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>45727</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>45819</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>44966</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>46269</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>46269</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>45665</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>46268</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>46269</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>46273</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>46273</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>46234</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>46281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>46281</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>46279</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>45791</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>46269</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>45791</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>45791</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>46280</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>45378</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>45574</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>46237</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32599,7 +32599,7 @@
         <v>45791</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>45336</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45804</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>45805</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>45804</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>45476</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>45352</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>45813</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45320</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>45741</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>45825</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45824</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>45825</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>45824</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>45740</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45835</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>45839</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>45839</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45771</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>45849</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45736</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>45852</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45852</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>45852</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45200</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>44829</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>44481</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>44818</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>45561</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44545</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>44767</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>44767</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>44982</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>45365</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>45271</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>44949</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>45271</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45313</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45713</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>45597</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45622</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>45873</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>44831</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45877</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>45771</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>44868</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>44895</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45300</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>44522</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36186,7 +36186,7 @@
         <v>45300</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>45425</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>45428</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>44895</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>45554</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>45355</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>45300</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>44470</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45847</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>46042</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36916,7 +36916,7 @@
         <v>46042</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>46042</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>46154</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>46154</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37208,7 +37208,7 @@
         <v>46264</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>

--- a/Översikt VARBERG.xlsx
+++ b/Översikt VARBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45688</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44834</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>46188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>44834</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44834</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44768</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45734</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>46281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>46281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45510</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45343</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45434</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45713</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45908</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>44860</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45840</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45198</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44657</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45352</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44918</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>46174</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>45141</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>44831</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>46188</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>45181</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45744</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>46281</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45251</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44469</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>45680</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>44655</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45300</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45324</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44722</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>44615</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>44473</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>44509</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44575</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44862</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>44504</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44581</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>44868</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>44834</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>44466</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>44691</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>44641</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>44797</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44657</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>44588</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44876</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44876</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44638</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44466</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44699</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44834</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44886</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44684</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44588</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44596</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44684</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44811</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45705</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44774</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45411</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45300</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45359</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>44890</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45411</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45574</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45436</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45884</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45323</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>46014</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>46014</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45097</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45097</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>46014</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>46014</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>46014</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>46024</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44894</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44867</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45336</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>45845</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45888</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45246</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45246</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45246</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45580</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44574</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45851</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45561</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>45897</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>46047</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>46047</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>45884</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45567</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45905</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45908</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45372</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>44615</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45910</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>46055</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>46055</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45909</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45911</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45912</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45742</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45359</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45804</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44910</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>46064</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>45804</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45432</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>45925</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45929</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>45929</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>45932</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>45932</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45805</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45476</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45392</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>44659</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45589</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45208</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>44974</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45938</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45352</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>46092</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>46094</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>46094</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>45945</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>44980</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>45007</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>45945</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>46104</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>45770</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>45952</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45583</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>46106</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>46106</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45954</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45741</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44966</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45960</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45960</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45579</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45960</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>46120</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45609</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44740</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45813</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45971</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>45058</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45131</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45741</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>45320</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45271</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>46132</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45973</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45978</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45096</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45980</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45979</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45600</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45985</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45985</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45487</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45637</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>44649</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45905</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>44649</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45986</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>45988</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>45706</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45706</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>44644</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>45994</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45994</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45994</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45852</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45701</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45743</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45700</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>45085</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45104</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>46003</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45554</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>46003</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45743</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45623</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>46007</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>46007</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>46007</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>46008</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>46007</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45706</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45743</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45477</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>46010</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>46008</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44970</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45772</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45932</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>45824</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45196</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45824</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45509</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45054</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45825</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45055</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45785</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45197</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45075</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45825</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45792</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45929</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45740</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45246</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45722</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45722</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45210</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>44734</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45744</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45085</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45058</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45455</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45275</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>45881</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>45369</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>44935</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45404</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>45722</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45835</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>45932</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>46161</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>44470</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>45839</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>45839</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>46161</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>46161</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45771</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>46164</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>45336</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>46164</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44896</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>45344</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45590</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45580</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45852</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>45849</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>45852</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45852</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45736</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>46168</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>44985</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>44827</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>44543</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>46175</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>46175</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>46174</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45743</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>44980</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>46174</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44595</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45281</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>44607</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>44981</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>45593</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>44949</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>44533</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44481</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45200</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45597</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>46182</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45561</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45271</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>44545</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>44982</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45574</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>46188</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>46188</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44829</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45271</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>46188</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45365</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>45582</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>45313</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>45622</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>44767</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>44767</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45713</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45422</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45873</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45434</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45722</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>45487</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>44818</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44831</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>46190</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>46190</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45349</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>44967</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>45086</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45075</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>46196</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45877</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>46196</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>46196</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>46199</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>46141</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>46202</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>46202</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>46198</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45727</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>45771</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>45672</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>46204</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44649</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45366</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>45638</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>46251</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>46251</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45182</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45600</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45600</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>46254</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46210</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45708</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>46210</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>46210</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>46210</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45915</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>46255</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45140</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45140</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>44711</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45261</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>46255</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44649</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45607</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45177</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45361</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>45197</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45695</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45401</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45159</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45315</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45279</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45328</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>46268</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45397</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45513</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45717</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>45758</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>45313</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>46269</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>46273</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>44851</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>46273</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>45272</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>46234</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45401</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>46237</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45259</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>46280</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>46269</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45238</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>46281</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>46281</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45642</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>45720</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>46279</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45400</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44622</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>46286</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>44620</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44657</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>44896</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>46288</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45222</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>44470</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45819</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>46269</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>46269</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>44855</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>45302</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>44770</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44904</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45140</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45155</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45014</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>44886</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>45013</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>44797</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>44981</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>45582</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>44722</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>44749</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>44628</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>44981</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44511</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45469</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>45734</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>44659</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>45574</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>45058</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45762</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45587</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45090</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45302</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>44641</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45635</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45665</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45224</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45539</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44875</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45224</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>44652</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>45762</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45769</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45665</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45678</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44935</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45436</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>45736</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>44811</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44837</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45457</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>45531</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45364</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>45364</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>45300</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>45722</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>45740</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>45737</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45341</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>45749</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45716</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>45754</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45184</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>45310</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>45791</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45378</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45791</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>45791</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45574</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>45791</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44868</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>44895</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45300</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44522</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>45300</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>45425</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45428</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>44895</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45554</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45355</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>45300</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>44470</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45847</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>46042</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>46042</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>46042</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>46154</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>46154</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>46264</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>

--- a/Översikt VARBERG.xlsx
+++ b/Översikt VARBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45688</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44834</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>46188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>44834</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44834</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44768</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45734</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>46281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>46281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45510</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45343</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45434</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45713</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45908</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>44860</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45840</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45198</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44657</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45352</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44918</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>46174</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>45141</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>44831</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>46188</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>45181</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45744</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>46281</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45251</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44469</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>45680</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>44655</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45300</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45324</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44722</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>44615</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>44473</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>44509</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44575</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44862</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>44504</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44581</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>44868</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>44834</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>44466</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>44691</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>44641</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>44797</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44657</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>44588</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44876</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44876</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44638</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44466</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44699</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44834</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44886</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44684</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44588</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44596</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44684</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44811</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45705</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44774</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45411</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45300</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45359</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>44890</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45411</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45574</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45436</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45884</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45323</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>46014</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>46014</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45097</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45097</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>46014</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>46014</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>46014</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>46024</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44894</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44867</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45336</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>45845</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45888</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45246</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45246</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45246</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45580</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44574</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45851</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45561</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>45897</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>46047</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>46047</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>45884</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45567</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45905</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45908</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45372</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>44615</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45910</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>46055</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>46055</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45909</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45911</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45912</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45742</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45359</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45804</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44910</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>46064</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>45804</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45432</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>45925</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45929</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>45929</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>45932</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>45932</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45805</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45476</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45392</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>44659</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45589</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45208</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>44974</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45938</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45352</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>46092</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>46094</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>46094</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>45945</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>44980</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>45007</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>45945</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>46104</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>45770</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>45952</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45583</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>46106</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>46106</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45954</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45741</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44966</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45960</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45960</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45579</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45960</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>46120</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45609</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44740</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45813</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45971</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>45058</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45131</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45741</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>45320</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45271</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>46132</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45973</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45978</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45096</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45980</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45979</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45600</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45985</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45985</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45487</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45637</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>44649</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45905</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>44649</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45986</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>45988</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>45706</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45706</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>44644</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>45994</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45994</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45994</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45852</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45701</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45743</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45700</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>45085</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45104</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>46003</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45554</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>46003</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45743</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45623</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>46007</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>46007</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>46007</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>46008</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>46007</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45706</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45743</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45477</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>46010</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>46008</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44970</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45772</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45932</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>45824</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45196</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45824</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45509</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45054</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45825</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45055</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45785</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45197</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45075</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45825</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45792</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45929</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45740</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45246</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45722</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45722</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45210</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>44734</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45744</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45085</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45058</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45455</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45275</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>45881</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>45369</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>44935</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45404</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>45722</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45835</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>45932</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>46161</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>44470</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>45839</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>45839</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>46161</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>46161</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45771</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>46164</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>45336</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>46164</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44896</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>45344</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45590</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45580</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45852</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>45849</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>45852</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45852</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45736</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>46168</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>44985</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>44827</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>44543</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>46175</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>46175</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>46174</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45743</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>44980</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>46174</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44595</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45281</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>44607</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>44981</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>45593</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>44949</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>44533</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44481</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45200</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45597</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>46182</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45561</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45271</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>44545</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>44982</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45574</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>46188</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>46188</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44829</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45271</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>46188</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45365</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>45582</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>45313</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>45622</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>44767</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>44767</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45713</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45422</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45873</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45434</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45722</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>45487</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>44818</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44831</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>46190</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>46190</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45349</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>44967</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>45086</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45075</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>46196</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45877</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>46196</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>46196</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>46199</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>46141</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>46202</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>46202</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>46198</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45727</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>45771</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>45672</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>46204</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44649</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45366</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>45638</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>46251</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>46251</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45182</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45600</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45600</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>46254</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46210</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45708</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>46210</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>46210</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>46210</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45915</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>46255</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45140</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45140</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>44711</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45261</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>46255</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44649</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45607</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45177</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45361</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>45197</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45695</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45401</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45159</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45315</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45279</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45328</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>46268</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45397</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45513</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45717</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>45758</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>45313</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>46269</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>46273</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>44851</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>46273</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>45272</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>46234</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45401</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>46237</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45259</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>46280</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>46269</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45238</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>46281</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>46281</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45642</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>45720</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>46279</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45400</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44622</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>46286</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>44620</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44657</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>44896</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>46288</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45222</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>44470</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45819</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>46269</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>46269</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>44855</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>45302</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>44770</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44904</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45140</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45155</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45014</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>44886</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>45013</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>44797</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>44981</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>45582</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>44722</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>44749</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>44628</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>44981</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44511</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45469</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>45734</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>44659</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>45574</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>45058</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45762</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45587</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45090</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45302</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>44641</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45635</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45665</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45224</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45539</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44875</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45224</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>44652</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>45762</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45769</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45665</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45678</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44935</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45436</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>45736</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>44811</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44837</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45457</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>45531</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45364</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>45364</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>45300</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>45722</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>45740</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>45737</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45341</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>45749</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45716</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>45754</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45184</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>45310</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>45791</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45378</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45791</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>45791</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45574</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>45791</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44868</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>44895</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45300</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44522</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>45300</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>45425</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45428</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>44895</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45554</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45355</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>45300</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>44470</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45847</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>46042</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>46042</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>46042</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>46154</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>46154</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>46264</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>

--- a/Översikt VARBERG.xlsx
+++ b/Översikt VARBERG.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45688</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>46188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>44834</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44834</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44768</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>46281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>46281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45734</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>44918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45352</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45680</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>45713</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45908</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45434</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44860</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45744</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>45840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45343</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>44831</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45141</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44657</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>46174</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>46188</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45181</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>46281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45198</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>45300</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>44655</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45324</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44722</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44615</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44473</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44509</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44575</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44862</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44504</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44581</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44868</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44834</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44691</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44641</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44797</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44657</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44876</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44638</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44699</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44834</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44886</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>44874</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44684</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44588</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44596</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44684</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44811</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>44980</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45271</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>44970</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45054</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45097</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>44902</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>45642</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>45097</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>45341</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44774</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>45259</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>46003</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45313</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>45737</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>46003</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45791</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45791</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>46007</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>46007</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>45791</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>45609</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>46007</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>46007</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44740</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>45884</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45300</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>46008</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45741</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45720</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45583</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>46010</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>46014</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>46014</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>46014</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>46014</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>46014</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>45378</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>45845</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>45888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>45743</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>45672</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>45580</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>46024</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>45336</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>45574</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44896</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>45851</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45455</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45897</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>44875</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45574</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45884</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45749</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>44649</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>45905</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45910</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45909</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45908</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45561</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45911</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45791</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45912</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45487</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>46047</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45336</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>46047</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45372</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45804</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45805</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45804</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>46055</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>44894</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>46055</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45769</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45925</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>45929</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44649</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44935</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>44981</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>45929</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45182</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45932</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>46064</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45932</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45469</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45539</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45938</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45323</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>45945</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>45310</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45945</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45600</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45945</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>45476</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>45352</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44543</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>45401</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45952</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45600</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45954</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45813</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45411</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>45960</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>46092</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45058</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44574</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45960</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45007</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45320</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>44974</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45736</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>46094</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>46094</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>44980</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44649</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45971</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45973</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45208</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>46104</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44886</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>46106</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45979</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45978</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45741</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45980</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>46106</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>45665</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45315</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45985</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45985</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>45986</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>45825</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45824</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>45988</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>44711</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>46120</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45825</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>45824</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>45582</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45994</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>45994</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>45740</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>45085</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45159</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>46132</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45487</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45275</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>45085</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>45835</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>45742</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>45574</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45364</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45364</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45839</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>45839</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>45104</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>44622</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>45623</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>45771</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45905</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45554</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45849</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>44827</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45736</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45392</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>45477</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44837</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45932</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45436</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45852</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>45852</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>45852</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45635</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>45222</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>45695</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>45589</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44867</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>45075</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>45852</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>45055</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>45785</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45929</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45246</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45436</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45328</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44749</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45279</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45743</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>44615</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45792</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45587</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45758</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45090</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45200</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>44829</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>44481</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>44818</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>45561</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>44545</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44511</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>44767</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>44767</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>45401</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>45400</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>45224</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>44896</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45300</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>45513</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>44935</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>44659</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44982</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45261</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45365</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>44620</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>44595</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>45271</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>44949</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>45271</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45313</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45713</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>45597</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>45622</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45873</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44831</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>44967</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>44904</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45881</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44641</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45404</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45246</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45246</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45359</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>46161</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>46161</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>45932</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>46161</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45593</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>45722</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>44811</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>45734</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45717</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45302</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>46164</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>46164</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45877</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45705</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>46168</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>45590</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45580</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>44797</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>46174</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>44910</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>45771</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>46174</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>44644</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>44649</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>46175</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>46175</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>45740</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46182</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45638</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>44628</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>46188</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>46188</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45722</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>46188</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44981</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45366</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44652</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>46190</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>44657</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45075</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>46190</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45678</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45359</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>46196</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>46196</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>46196</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45574</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45197</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45701</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>46202</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>44533</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44659</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46202</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>46141</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>46199</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45281</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45210</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>44851</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>46198</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>46204</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>46210</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>46210</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>46210</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>46210</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45349</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45915</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>45582</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>45411</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45238</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45600</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45361</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45607</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>45509</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45369</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>44734</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45302</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45224</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45155</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>46268</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46269</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45140</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45140</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>46273</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>45058</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>46273</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45434</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>46234</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45196</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>46281</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>46281</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>46269</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>45197</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>46280</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45706</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>45762</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>46237</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>45397</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45772</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45700</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>45722</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>44770</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>44985</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>45422</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>44890</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45246</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>45140</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>46286</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>45014</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>45819</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>45567</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>45344</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>46269</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>46269</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>46288</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>45716</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>45770</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45708</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45579</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>45457</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>45744</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>46251</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>46251</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>46295</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>44855</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44981</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>46295</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44722</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>46255</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45272</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>46255</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>46254</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>46279</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45743</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45743</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45531</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45058</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>45184</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>45013</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45177</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>44607</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45722</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>45722</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45432</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45096</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45706</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>45706</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45086</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45754</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45637</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45131</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45762</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45727</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44966</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45665</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>44868</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44895</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45300</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44522</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45300</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>45425</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>45428</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>44895</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45554</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45355</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45300</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45847</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>46042</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>46042</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>46042</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>46154</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>46154</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>46264</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>

--- a/Översikt VARBERG.xlsx
+++ b/Översikt VARBERG.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45688</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>46188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>44834</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44834</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44768</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>46281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>46281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45734</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>44918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45352</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45680</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>45713</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45908</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45434</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44860</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45744</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>45840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45343</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>44831</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45141</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44657</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>46174</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>46188</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45181</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>46281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45198</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>45300</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>44655</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45324</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44722</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44615</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44473</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44509</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44575</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44862</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44504</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44581</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44868</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44834</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44691</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44641</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44797</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44657</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44876</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44638</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44699</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44834</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44886</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>44874</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44684</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44588</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44596</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44684</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44811</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>44980</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45271</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>44970</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45054</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45097</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>44902</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>45642</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>45097</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>45341</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44774</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>45259</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>46003</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45313</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>45737</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>46003</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45791</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45791</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>46007</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>46007</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>45791</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>45609</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>46007</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>46007</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44740</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>45884</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45300</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>46008</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45741</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45720</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45583</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>46010</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>46014</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>46014</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>46014</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>46014</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>46014</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>45378</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>45845</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>45888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>45743</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>45672</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>45580</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>46024</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>45336</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>45574</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44896</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>45851</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45455</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45897</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>44875</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45574</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45884</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45749</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>44649</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>45905</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45910</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45909</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45908</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45561</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45911</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45791</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45912</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45487</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>46047</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45336</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>46047</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45372</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45804</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45805</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45804</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>46055</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>44894</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>46055</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45769</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45925</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>45929</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44649</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44935</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>44981</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>45929</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45182</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45932</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>46064</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45932</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45469</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45539</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45938</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45323</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>45945</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>45310</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45945</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45600</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45945</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>45476</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>45352</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44543</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>45401</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45952</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45600</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45954</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45813</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45411</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>45960</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>46092</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45058</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44574</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45960</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45007</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45320</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>44974</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45736</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>46094</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>46094</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>44980</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44649</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45971</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45973</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45208</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>46104</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44886</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>46106</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45979</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45978</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45741</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45980</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>46106</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>45665</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45315</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45985</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45985</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>45986</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>45825</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45824</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>45988</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>44711</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>46120</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45825</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>45824</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>45582</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45994</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>45994</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>45740</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>45085</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45159</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>46132</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45487</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45275</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>45085</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>45835</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>45742</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>45574</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45364</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45364</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45839</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>45839</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>45104</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>44622</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>45623</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>45771</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45905</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45554</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45849</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>44827</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45736</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45392</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>45477</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44837</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45932</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45436</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45852</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>45852</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>45852</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45635</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>45222</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>45695</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>45589</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44867</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>45075</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>45852</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>45055</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>45785</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45929</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45246</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45436</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45328</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44749</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45279</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45743</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>44615</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45792</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45587</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45758</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45090</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45200</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>44829</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>44481</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>44818</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>45561</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>44545</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44511</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>44767</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>44767</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>45401</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>45400</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>45224</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>44896</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45300</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>45513</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>44935</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>44659</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44982</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45261</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45365</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>44620</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>44595</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>45271</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>44949</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>45271</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45313</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45713</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>45597</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>45622</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45873</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44831</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>44967</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>44904</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45881</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44641</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45404</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45246</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45246</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45359</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>46161</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>46161</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>45932</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>46161</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45593</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>45722</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>44811</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>45734</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45717</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45302</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>46164</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>46164</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45877</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45705</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>46168</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>45590</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45580</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>44797</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>46174</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>44910</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>45771</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>46174</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>44644</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>44649</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>46175</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>46175</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>45740</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46182</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45638</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>44628</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>46188</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>46188</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45722</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>46188</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44981</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45366</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44652</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>46190</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>44657</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45075</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>46190</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45678</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45359</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>46196</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>46196</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>46196</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45574</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45197</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45701</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>46202</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>44533</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44659</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46202</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>46141</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>46199</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45281</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45210</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>44851</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>46198</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>46204</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>46210</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>46210</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>46210</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>46210</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45349</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45915</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>45582</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>45411</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45238</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45600</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45361</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45607</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>45509</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45369</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>44734</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45302</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45224</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45155</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>46268</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46269</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45140</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45140</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>46273</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>45058</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>46273</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45434</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>46234</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45196</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>46281</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>46281</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>46269</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>45197</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>46280</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45706</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>45762</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>46237</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>45397</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45772</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45700</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>45722</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>44770</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>44985</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>45422</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>44890</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45246</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>45140</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>46286</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>45014</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>45819</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>45567</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>45344</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>46269</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>46269</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>46288</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>45716</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>45770</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45708</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45579</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>45457</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>45744</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>46251</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>46251</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>46295</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>44855</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44981</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>46295</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44722</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>46255</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45272</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>46255</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>46254</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>46279</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45743</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45743</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45531</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45058</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>45184</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>45013</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45177</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>44607</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45722</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>45722</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45432</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45096</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45706</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>45706</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45086</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45754</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45637</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45131</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45762</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45727</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44966</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45665</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>44868</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44895</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45300</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44522</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45300</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>45425</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>45428</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>44895</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45554</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45355</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45300</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45847</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>46042</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>46042</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>46042</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>46154</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>46154</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>46264</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>

--- a/Översikt VARBERG.xlsx
+++ b/Översikt VARBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45688</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44834</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>46188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>44834</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44834</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44768</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45734</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45510</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>46281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>46281</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45352</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>44918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45343</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45713</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45908</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45141</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44860</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>45434</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>45181</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45198</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44831</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>44812</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45744</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>44657</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45251</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>46174</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>46188</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46281</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44655</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45324</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44722</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44615</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44862</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44504</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44581</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44868</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44834</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44876</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44876</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44638</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44588</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44691</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44699</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44641</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44797</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44684</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44596</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>44886</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44657</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44588</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44684</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44659</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>45574</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45058</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45762</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>44811</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45587</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45085</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>45090</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45359</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>45436</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>45058</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>45705</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>45455</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>45302</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>44774</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>45275</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>45369</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44935</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44641</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44890</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45635</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45665</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>45224</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45411</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>45539</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45300</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45574</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44875</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45224</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45336</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>44652</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>45411</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>44896</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45771</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45344</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45762</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>45769</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45665</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45678</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44985</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44902</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45884</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44935</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45323</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>45097</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>45097</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45436</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>45736</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44811</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44827</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44894</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44837</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45845</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45888</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44543</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45457</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>45531</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>45743</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>44867</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45580</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>45364</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>45364</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45300</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44980</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45851</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45722</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45897</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45740</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>45737</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45246</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45246</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45246</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45884</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45341</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>44574</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>44595</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>45749</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45716</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45281</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>44607</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45905</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>45754</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45561</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45184</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45310</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44981</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45910</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45593</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45909</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45911</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>45246</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45912</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>45567</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>44533</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44615</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>45574</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45582</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45742</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>45422</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>45359</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44910</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>45434</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>45722</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>45487</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45349</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44967</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45925</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45086</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45791</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45075</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45432</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45378</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45791</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45791</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45574</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>45791</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>45929</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45929</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45932</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45392</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>44659</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>45932</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45589</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45336</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45727</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45208</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44974</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45672</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44649</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>45366</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45804</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45804</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45638</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44980</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45007</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>45805</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45938</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45476</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45770</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45182</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45352</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45583</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>45600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45600</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45945</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45945</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45741</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>45813</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45708</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>45945</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>45741</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>45320</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>44966</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45579</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45140</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45140</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45824</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45824</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44711</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45261</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>45825</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45825</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45952</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45609</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45740</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>44649</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>44740</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45058</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45177</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45954</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>45131</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45960</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>45960</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45960</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>45271</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45096</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>45600</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>45839</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>45839</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45197</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45695</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45637</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>44649</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>44649</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45401</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>45971</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45771</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45159</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>45315</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45279</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>45706</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45706</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>44644</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45852</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45849</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45852</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>45973</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45852</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>45736</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>45978</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>45701</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45700</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>45085</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45328</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45397</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45513</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>45717</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44949</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45758</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44481</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45980</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45200</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45597</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45313</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45561</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45743</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45271</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44545</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>45979</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44982</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>44829</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45271</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45706</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45365</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45313</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45622</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45743</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>44767</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>44767</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45713</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44851</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45873</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44818</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>44831</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45877</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44970</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>45772</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>45272</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45196</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46094</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45401</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45509</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45054</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>45259</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45985</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45055</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45197</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45075</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>46104</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45238</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45986</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45246</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>46106</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>46106</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>45722</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45722</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>45642</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45988</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>45210</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44734</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>45720</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>45744</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>46120</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>45994</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45994</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45400</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>45994</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44622</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>44620</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44657</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44896</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>46132</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45222</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>46003</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>46003</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>44855</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>45302</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27202,7 +27202,7 @@
         <v>44770</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>45487</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>45905</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>44904</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>46007</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45140</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>46007</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>46007</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>46008</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>46007</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>45155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45014</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44886</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>46010</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45013</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>46008</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>46014</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>46014</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>46014</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>46014</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>46014</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45852</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>44797</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>46024</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>45743</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45104</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44981</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45554</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45623</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45582</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44722</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45477</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>44749</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44628</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45932</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44981</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>44511</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>46047</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45469</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45734</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>46047</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45785</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>45792</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45929</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45372</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>46055</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46055</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>46064</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45881</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45404</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45722</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>46092</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45932</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>46161</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>46094</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>46161</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46161</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>46164</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>46164</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45590</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45580</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>46168</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>46175</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>46175</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>46174</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>46174</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>46182</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>46188</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>46188</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>46188</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>46190</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>46190</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>46196</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32531,7 +32531,7 @@
         <v>46196</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>46196</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>46199</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>46141</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>46202</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>46202</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>46198</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>46204</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>46210</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>46210</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>46210</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>46210</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>45915</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>45607</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>45361</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>46268</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>46269</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>46273</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>46273</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>46234</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>46237</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>46280</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>46269</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>46281</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>46281</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>46286</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>46288</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45819</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>46251</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>46251</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>46295</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>46279</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>46295</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45835</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>46254</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>46255</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>46299</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>46255</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>46300</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>46269</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>46269</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>46301</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>46303</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>44868</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44895</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45300</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>44522</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>45300</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45425</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45428</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44895</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45554</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45355</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45300</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45847</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>46042</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>46042</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>46042</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>46154</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>46154</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>46264</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>

--- a/Översikt VARBERG.xlsx
+++ b/Översikt VARBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45688</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44834</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>46188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>44834</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44834</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44768</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45734</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45510</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>46281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>46281</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45352</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>44918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45343</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45713</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45908</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45141</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44860</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>45434</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>45181</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45198</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44831</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>44812</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45744</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>44657</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45251</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>46174</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>46188</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46281</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44655</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45324</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44722</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44615</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44862</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44504</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44581</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44868</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44834</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44876</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44876</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44638</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44588</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44691</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44699</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44641</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44797</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44684</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44596</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>44886</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44657</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44588</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44684</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44659</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>45574</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45058</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45762</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>44811</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45587</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45085</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>45090</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45359</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>45436</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>45058</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>45705</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>45455</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>45302</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>44774</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>45275</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>45369</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44935</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44641</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44890</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45635</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45665</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>45224</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45411</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>45539</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45300</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45574</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44875</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45224</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45336</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>44652</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>45411</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>44896</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45771</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45344</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45762</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>45769</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45665</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45678</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44985</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44902</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45884</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44935</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45323</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>45097</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>45097</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45436</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>45736</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44811</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44827</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44894</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44837</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45845</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45888</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44543</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45457</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>45531</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>45743</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>44867</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45580</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>45364</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>45364</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45300</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44980</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45851</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45722</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45897</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45740</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>45737</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45246</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45246</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45246</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45884</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45341</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>44574</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>44595</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>45749</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45716</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45281</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>44607</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45905</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>45754</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45561</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45184</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45310</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44981</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45910</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45593</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45909</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45911</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>45246</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45912</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>45567</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>44533</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44615</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>45574</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45582</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45742</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>45422</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>45359</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44910</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>45434</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>45722</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>45487</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45349</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44967</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45925</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45086</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45791</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45075</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45432</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45378</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45791</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45791</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45574</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>45791</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>45929</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45929</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45932</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45392</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>44659</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>45932</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45589</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45336</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45727</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45208</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44974</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45672</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44649</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>45366</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45804</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45804</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45638</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44980</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45007</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>45805</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45938</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45476</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45770</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45182</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45352</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45583</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>45600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45600</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45945</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45945</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45741</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>45813</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45708</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>45945</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>45741</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>45320</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>44966</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45579</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45140</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45140</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45824</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45824</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44711</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45261</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>45825</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45825</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45952</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45609</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45740</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>44649</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>44740</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45058</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45177</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45954</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>45131</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45960</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>45960</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45960</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>45271</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45096</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>45600</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>45839</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>45839</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45197</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45695</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45637</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>44649</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>44649</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45401</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>45971</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45771</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45159</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>45315</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45279</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>45706</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45706</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>44644</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45852</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45849</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45852</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>45973</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45852</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>45736</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>45978</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>45701</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45700</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>45085</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45328</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45397</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45513</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>45717</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44949</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45758</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44481</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45980</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45200</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45597</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45313</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45561</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45743</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45271</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44545</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>45979</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44982</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>44829</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45271</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45706</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45365</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45313</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45622</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45743</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>44767</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>44767</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45713</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44851</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45873</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44818</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>44831</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45877</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44970</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>45772</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>45272</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45196</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46094</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45401</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45509</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45054</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>45259</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45985</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45055</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45197</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45075</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>46104</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45238</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45986</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45246</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>46106</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>46106</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>45722</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45722</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>45642</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45988</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>45210</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44734</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>45720</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>45744</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>46120</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>45994</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45994</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45400</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>45994</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44622</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>44620</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44657</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44896</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>46132</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45222</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>46003</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>46003</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>44855</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>45302</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27202,7 +27202,7 @@
         <v>44770</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>45487</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>45905</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>44904</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>46007</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45140</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>46007</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>46007</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>46008</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>46007</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>45155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45014</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44886</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>46010</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45013</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>46008</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>46014</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>46014</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>46014</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>46014</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>46014</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45852</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>44797</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>46024</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>45743</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45104</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44981</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45554</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45623</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45582</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44722</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45477</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>44749</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44628</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45932</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44981</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>44511</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>46047</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45469</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45734</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>46047</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45785</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>45792</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45929</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45372</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>46055</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46055</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>46064</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45881</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45404</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45722</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>46092</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45932</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>46161</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>46094</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>46161</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46161</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>46164</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>46164</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45590</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45580</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>46168</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>46175</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>46175</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>46174</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>46174</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>46182</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>46188</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>46188</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>46188</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>46190</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>46190</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>46196</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32531,7 +32531,7 @@
         <v>46196</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>46196</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>46199</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>46141</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>46202</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>46202</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>46198</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>46204</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>46210</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>46210</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>46210</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>46210</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>45915</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>45607</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>45361</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>46268</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>46269</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>46273</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>46273</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>46234</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>46237</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>46280</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>46269</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>46281</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>46281</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>46286</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>46288</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45819</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>46251</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>46251</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>46295</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>46279</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>46295</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45835</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>46254</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>46255</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>46299</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>46255</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>46300</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>46269</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>46269</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>46301</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>46303</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>44868</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44895</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45300</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>44522</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>45300</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45425</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45428</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44895</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45554</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45355</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45300</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45847</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>46042</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>46042</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>46042</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>46154</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>46154</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>46264</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>

--- a/Översikt VARBERG.xlsx
+++ b/Översikt VARBERG.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45688</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46188</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>44834</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44834</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44768</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>46281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>46281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45734</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>44918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45352</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45680</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>45840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>45713</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>45908</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45744</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>45343</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45141</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>46174</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44657</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>45181</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>46188</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>46281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>45198</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45434</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44831</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>45300</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>44655</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45324</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44722</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44615</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44862</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44504</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44581</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44868</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44834</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44691</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44641</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44657</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44588</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44876</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44638</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44699</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44886</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>44684</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44588</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44596</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44684</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44811</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44980</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>44902</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44970</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45271</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45097</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45054</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>45642</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>45097</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>45259</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44774</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45341</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>45300</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45609</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45741</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>45720</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44740</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45583</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45743</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>45672</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45455</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45336</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45749</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45574</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44649</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44875</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45561</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45487</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45313</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45737</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44894</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45769</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44649</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>44935</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44981</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45539</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45469</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45310</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45600</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45323</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>45600</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44543</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45401</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45182</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45411</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45058</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45007</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>44574</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>44974</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45736</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44980</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>44649</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>44886</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45208</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45665</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45315</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45623</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45884</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45554</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44711</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45477</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45932</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45582</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45845</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45888</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45580</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45085</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45159</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45851</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45897</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45852</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45785</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45929</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45275</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45743</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>45792</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>45085</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45884</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45742</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>45905</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45910</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>45909</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45908</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45364</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45364</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>45911</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45912</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>44622</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44827</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>45925</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45392</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>44837</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45929</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>45436</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>45635</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45932</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45932</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45222</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45695</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45589</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45938</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44867</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45945</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45945</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45075</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>45945</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45055</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45246</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45881</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45436</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45328</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>45954</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>44749</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45404</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45960</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45960</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45279</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44615</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45587</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45758</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45960</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45090</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>46161</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>46161</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45932</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>46161</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44511</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45722</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45971</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45401</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45973</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45400</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45224</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>44896</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45300</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45513</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>44935</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>44659</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>45261</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44620</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45979</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44595</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45978</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45980</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>46164</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44967</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>46164</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45985</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>44904</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45986</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44641</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45246</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45246</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45246</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45359</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45988</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45593</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>46168</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44811</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45590</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45734</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45717</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45994</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45994</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45994</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45302</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45580</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>46003</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>45705</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>46003</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>46007</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>46007</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>46007</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46007</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>44797</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46008</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>46174</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44910</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44644</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44649</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>46010</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46014</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46014</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>46014</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>46014</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>46014</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>46174</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>46008</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45740</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>46024</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45638</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44628</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>46175</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>46175</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45722</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>44981</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45366</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44652</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>44657</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45075</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>46047</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>46047</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45372</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45678</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>46182</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>46055</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>45359</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>46055</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>45574</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>45197</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>46064</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>45701</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44533</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>46188</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44659</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>46188</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45281</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>45210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>44851</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>46188</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>46190</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>46092</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>46190</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45349</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>46094</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45582</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45411</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45238</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45600</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45509</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45369</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>46104</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>46196</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>44734</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>46106</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>45302</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>46196</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>46196</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>45224</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>46106</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>45155</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>46202</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>46120</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>46202</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45140</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45140</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>46141</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45058</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>46199</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>46132</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>45487</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>45434</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>46198</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>45196</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>46204</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45197</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>45706</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>45762</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>45397</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45104</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26228,7 +26228,7 @@
         <v>45772</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>45700</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45722</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>46210</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44770</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44985</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>46210</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>46210</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>46210</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>45422</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>45915</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>44890</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>45246</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>45361</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>45607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45140</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45014</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45567</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45344</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>46273</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45716</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>46273</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45770</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45708</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45579</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45457</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45744</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46234</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>46281</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44855</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>46281</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44981</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>46280</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>44722</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>46237</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>45272</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45743</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>45743</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>45531</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45058</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45184</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>45013</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>46286</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45177</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44607</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45819</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>46288</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45722</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45722</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45432</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45096</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45706</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45706</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>45086</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>46251</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45754</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>46251</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45637</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>46295</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46295</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45131</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45762</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45727</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>44966</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>46254</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>46279</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45665</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>46255</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>46255</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46301</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45835</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>46300</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>46299</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>46303</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45791</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45791</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>45791</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>45378</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>45574</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45791</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>46307</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45336</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>45804</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>45805</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45804</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45476</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>45352</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45813</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>46268</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>45320</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>46269</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>46269</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45741</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>46311</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45825</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>45824</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45825</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45824</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>46269</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33490,7 +33490,7 @@
         <v>46269</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>45740</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45839</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>45839</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45771</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>45849</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45736</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45852</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>45852</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45852</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>45200</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>44829</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>44818</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45561</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>44545</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>44767</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>44767</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44982</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>45365</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45271</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44949</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45271</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45313</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45713</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45597</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45622</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>45873</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44831</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45877</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>45771</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>44868</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44895</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45300</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>44522</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>45300</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45425</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45428</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44895</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45554</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45355</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45300</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45847</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>46042</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>46042</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>46042</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>46154</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>46154</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>46264</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>

--- a/Översikt VARBERG.xlsx
+++ b/Översikt VARBERG.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45688</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46188</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>44834</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44834</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44768</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>46281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>46281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45734</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>44918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45352</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45680</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>45840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>45713</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>45908</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45744</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>45343</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45141</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>46174</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44657</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>45181</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>46188</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>46281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>45198</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45434</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44831</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>45300</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>44655</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45324</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44722</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44615</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44862</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44504</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44581</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44868</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44834</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44691</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44641</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44657</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44588</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44876</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44638</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44699</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44886</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>44684</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44588</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44596</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44684</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44811</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44980</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>44902</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44970</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45271</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45097</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45054</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>45642</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>45097</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>45259</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44774</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45341</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>45300</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45609</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45741</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>45720</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44740</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45583</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45743</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>45672</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45455</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45336</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45749</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45574</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44649</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44875</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45561</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45487</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45313</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45737</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44894</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45769</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44649</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>44935</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44981</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45539</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45469</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45310</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45600</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45323</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>45600</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44543</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45401</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45182</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45411</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45058</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45007</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>44574</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>44974</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45736</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44980</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>44649</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>44886</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45208</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45665</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45315</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45623</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45884</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45554</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44711</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45477</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45932</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45582</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45845</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45888</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45580</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45085</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45159</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45851</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45897</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45852</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45785</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45929</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45275</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45743</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>45792</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>45085</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45884</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45742</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>45905</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45910</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>45909</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45908</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45364</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45364</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>45911</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45912</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>44622</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44827</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>45925</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45392</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>44837</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45929</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>45436</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>45635</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45932</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45932</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45222</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45695</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45589</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45938</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44867</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45945</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45945</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45075</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>45945</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45055</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45246</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45881</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45436</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45328</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>45954</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>44749</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45404</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45960</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45960</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45279</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44615</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45587</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45758</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45960</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45090</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>46161</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>46161</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45932</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>46161</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44511</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45722</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45971</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45401</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45973</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45400</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45224</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>44896</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45300</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45513</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>44935</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>44659</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>45261</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44620</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45979</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44595</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45978</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45980</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>46164</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44967</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>46164</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45985</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>44904</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45986</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44641</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45246</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45246</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45246</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45359</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45988</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45593</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>46168</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44811</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45590</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45734</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45717</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45994</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45994</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45994</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45302</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45580</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>46003</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>45705</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>46003</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>46007</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>46007</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>46007</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46007</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>44797</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46008</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>46174</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44910</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44644</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44649</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>46010</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46014</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46014</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>46014</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>46014</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>46014</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>46174</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>46008</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45740</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>46024</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45638</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44628</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>46175</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>46175</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45722</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>44981</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45366</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44652</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>44657</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45075</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>46047</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>46047</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45372</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45678</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>46182</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>46055</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>45359</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>46055</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>45574</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>45197</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>46064</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>45701</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44533</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>46188</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44659</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>46188</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45281</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>45210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>44851</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>46188</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>46190</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>46092</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>46190</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45349</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>46094</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45582</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45411</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45238</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45600</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45509</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45369</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>46104</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>46196</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>44734</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>46106</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>45302</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>46196</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>46196</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>45224</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>46106</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>45155</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>46202</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>46120</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>46202</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45140</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45140</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>46141</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45058</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>46199</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>46132</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>45487</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>45434</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>46198</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>45196</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>46204</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45197</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>45706</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>45762</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>45397</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45104</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26228,7 +26228,7 @@
         <v>45772</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>45700</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45722</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>46210</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44770</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44985</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>46210</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>46210</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>46210</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>45422</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>45915</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>44890</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>45246</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>45361</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>45607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45140</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45014</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45567</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45344</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>46273</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45716</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>46273</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45770</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45708</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45579</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45457</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45744</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46234</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>46281</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44855</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>46281</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44981</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>46280</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>44722</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>46237</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>45272</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45743</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>45743</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>45531</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45058</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45184</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>45013</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>46286</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45177</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44607</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45819</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>46288</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45722</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45722</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45432</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45096</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45706</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45706</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>45086</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>46251</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45754</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>46251</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45637</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>46295</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46295</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45131</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45762</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45727</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>44966</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>46254</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>46279</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45665</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>46255</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>46255</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46301</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45835</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>46300</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>46299</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>46303</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45791</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45791</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>45791</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>45378</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>45574</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45791</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>46307</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45336</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>45804</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>45805</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45804</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45476</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>45352</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45813</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>46268</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>45320</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>46269</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>46269</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45741</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>46311</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45825</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>45824</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45825</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45824</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>46269</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33490,7 +33490,7 @@
         <v>46269</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>45740</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45839</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>45839</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45771</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>45849</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45736</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45852</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>45852</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45852</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>45200</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>44829</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>44818</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45561</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>44545</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>44767</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>44767</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44982</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>45365</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45271</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44949</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45271</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45313</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45713</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45597</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45622</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>45873</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44831</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45877</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>45771</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>44868</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44895</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45300</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>44522</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>45300</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45425</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45428</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44895</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45554</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45355</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45300</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45847</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>46042</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>46042</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>46042</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>46154</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>46154</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>46264</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>

--- a/Översikt VARBERG.xlsx
+++ b/Översikt VARBERG.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45688</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46188</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>44834</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44834</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44768</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45510</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45093</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>46281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>46281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45734</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45343</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45713</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45908</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45680</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>46174</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>46281</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45434</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>44831</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>45840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44860</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45198</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44657</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45352</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>45141</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44812</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45744</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44655</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45324</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44722</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44615</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44862</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44504</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44581</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44868</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44834</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44691</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44641</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44657</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44588</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44876</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44638</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44699</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44886</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>44684</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44588</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44596</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44684</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44811</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44855</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45302</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44770</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45845</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45888</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>44904</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>44774</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>45884</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>45580</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45140</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>45155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45851</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45014</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44886</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45300</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45013</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45897</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>45411</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45884</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>45905</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>45908</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44797</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>45910</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45722</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>45909</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45911</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45932</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>46161</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45912</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>46161</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44981</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>46161</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>46164</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45582</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>46164</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>44722</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45590</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45580</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44749</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>44628</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45925</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>46168</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45929</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45929</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45932</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>44981</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45932</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>44511</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45469</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>46175</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46175</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>46174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45734</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45359</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>45436</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45938</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>44659</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45574</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45058</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>46174</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45762</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45587</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45945</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45090</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>44890</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45945</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45411</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45574</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45945</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45952</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45302</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44641</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45954</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>46182</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45635</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45665</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45960</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45960</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45960</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45224</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>46188</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>46188</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>45539</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>46188</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>44875</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45224</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>44652</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>46190</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>46190</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>45971</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>45762</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>45769</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>45665</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45678</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>46196</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>44935</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>46196</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>46196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>45973</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45436</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>46199</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>45736</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>46141</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45980</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44811</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>46202</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>46202</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45979</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>46198</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44837</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>46204</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45457</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>45531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44902</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45985</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45364</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45364</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45986</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45300</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45722</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45740</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>45988</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45737</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>46210</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>46210</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>46210</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>46210</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45915</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45994</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45994</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45323</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45341</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45749</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45994</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45097</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45097</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45716</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45607</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45754</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45361</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>45184</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45310</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>46003</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>46003</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>46007</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>46007</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>46007</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>46008</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>46234</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>46007</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>46010</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>46237</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>46008</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>46014</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>46014</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>46280</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>46014</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>46014</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>46014</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>46281</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>46281</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>46024</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>45791</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45378</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>45791</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45791</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>45791</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19341,7 +19341,7 @@
         <v>46286</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>46288</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>45336</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45819</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>46047</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>46047</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45372</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>45804</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>45804</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>46055</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>46055</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45805</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>45476</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>45352</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>46251</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>44894</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45813</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45741</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45320</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>46064</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>46251</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>46295</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46279</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45824</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45824</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45825</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>45825</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45740</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>46295</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45835</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>46254</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>46255</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>46092</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>46299</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>46255</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45839</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>46094</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45839</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>44867</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45771</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>46300</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>46104</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>45852</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45849</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45852</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>46106</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45852</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>45736</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>46106</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>46301</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>46303</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>45246</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45246</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45246</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>46120</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>44949</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>44574</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>45200</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45597</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>45561</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45271</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44545</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>44982</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>44829</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45271</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45365</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45313</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45622</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44767</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44767</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45713</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45873</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>44818</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>44831</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>46132</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45877</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45771</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45561</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45567</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45487</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45905</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>46307</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44615</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45852</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>45742</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>45743</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>46269</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>45359</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45104</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>46269</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>44910</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>46268</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>46269</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>45554</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46269</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45623</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>46311</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45432</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45477</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>46273</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>46273</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>45932</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>46315</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>46315</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45785</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45392</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44659</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45792</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45929</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46317</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45589</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>46317</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45208</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44974</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44980</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45007</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45770</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>45583</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45741</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45881</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45404</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44966</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45579</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45609</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>44740</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45058</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45131</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45271</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45096</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45600</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45637</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44649</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44649</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45706</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45706</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>44644</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45701</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45700</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>45085</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45743</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45706</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45743</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44970</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45772</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45196</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45509</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>45054</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45055</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45197</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45075</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>45246</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45722</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>45722</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>45210</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44734</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45744</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45085</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45058</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45455</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45275</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45369</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>44935</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45336</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>44896</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45344</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44985</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>44827</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>44543</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45743</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>44980</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>44595</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45281</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>44607</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44981</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45593</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45246</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44533</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45574</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45582</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45422</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45434</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45722</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45487</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45349</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>44967</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45086</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45075</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45727</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45672</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44649</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45366</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45638</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>45182</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33490,7 +33490,7 @@
         <v>45600</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>45600</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45708</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>45140</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45140</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>44711</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45261</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>44649</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>45177</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45197</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>45695</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34298,7 +34298,7 @@
         <v>45401</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34371,7 +34371,7 @@
         <v>45159</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34444,7 +34444,7 @@
         <v>45315</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>45279</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45328</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>45397</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45513</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45717</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45758</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45313</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>44851</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45272</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45401</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45259</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45238</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45642</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45720</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>45400</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>44622</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35690,7 +35690,7 @@
         <v>44620</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35763,7 +35763,7 @@
         <v>44657</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>44896</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>45222</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>44868</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>44895</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>45300</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44522</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45300</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>45425</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45428</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44895</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>45554</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>45355</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>45300</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45847</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>46042</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>46042</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>46042</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>46154</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>46154</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>46264</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>

--- a/Översikt VARBERG.xlsx
+++ b/Översikt VARBERG.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45688</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46188</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>44834</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44834</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44768</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45510</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45093</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>46281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>46281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45734</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45343</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45713</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45908</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45680</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>46174</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>46281</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45434</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>44831</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>45840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44860</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45198</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44657</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45352</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>45141</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44812</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45744</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44655</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45324</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44722</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44615</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44862</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44504</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44581</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44868</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44834</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44691</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44641</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44657</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44588</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44876</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44638</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44699</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44886</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>44684</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44588</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44596</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44684</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44811</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44855</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45302</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44770</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45845</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45888</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>44904</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>44774</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>45884</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>45580</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45140</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>45155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45851</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45014</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44886</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45300</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45013</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45897</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>45411</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45884</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>45905</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>45908</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44797</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>45910</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45722</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>45909</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45911</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45932</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>46161</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45912</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>46161</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44981</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>46161</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>46164</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45582</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>46164</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>44722</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45590</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45580</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44749</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>44628</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45925</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>46168</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45929</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45929</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45932</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>44981</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45932</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>44511</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45469</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>46175</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46175</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>46174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45734</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45359</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>45436</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45938</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>44659</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45574</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45058</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>46174</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45762</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45587</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45945</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45090</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>44890</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45945</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45411</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45574</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45945</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45952</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45302</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44641</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45954</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>46182</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45635</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45665</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45960</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45960</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45960</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45224</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>46188</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>46188</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>45539</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>46188</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>44875</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45224</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>44652</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>46190</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>46190</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>45971</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>45762</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>45769</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>45665</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45678</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>46196</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>44935</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>46196</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>46196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>45973</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45436</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>46199</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>45736</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>46141</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45980</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44811</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>46202</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>46202</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45979</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>46198</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44837</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>46204</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45457</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>45531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44902</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45985</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45364</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45364</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45986</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45300</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45722</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45740</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>45988</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45737</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>46210</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>46210</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>46210</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>46210</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45915</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45994</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45994</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45323</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45341</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45749</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45994</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45097</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45097</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45716</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45607</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45754</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45361</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>45184</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45310</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>46003</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>46003</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>46007</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>46007</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>46007</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>46008</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>46234</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>46007</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>46010</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>46237</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>46008</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>46014</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>46014</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>46280</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>46014</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>46014</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>46014</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>46281</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>46281</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>46024</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>45791</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45378</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>45791</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45791</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>45791</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19341,7 +19341,7 @@
         <v>46286</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>46288</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>45336</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45819</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>46047</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>46047</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45372</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>45804</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>45804</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>46055</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>46055</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45805</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>45476</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>45352</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>46251</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>44894</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45813</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45741</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45320</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>46064</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>46251</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>46295</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46279</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45824</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45824</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45825</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>45825</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45740</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>46295</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45835</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>46254</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>46255</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>46092</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>46299</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>46255</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45839</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>46094</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45839</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>44867</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45771</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>46300</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>46104</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>45852</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45849</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45852</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>46106</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45852</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>45736</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>46106</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>46301</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>46303</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>45246</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45246</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45246</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>46120</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>44949</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>44574</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>45200</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45597</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>45561</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45271</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44545</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>44982</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>44829</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45271</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45365</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45313</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45622</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44767</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44767</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45713</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45873</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>44818</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>44831</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>46132</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45877</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45771</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45561</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45567</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45487</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45905</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>46307</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44615</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45852</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>45742</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>45743</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>46269</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>45359</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45104</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>46269</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>44910</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>46268</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>46269</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>45554</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46269</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45623</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>46311</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45432</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45477</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>46273</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>46273</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>45932</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>46315</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>46315</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45785</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45392</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44659</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45792</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45929</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46317</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45589</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>46317</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45208</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44974</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44980</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45007</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45770</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>45583</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45741</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45881</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45404</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44966</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45579</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45609</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>44740</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45058</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45131</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45271</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45096</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45600</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45637</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44649</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44649</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45706</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45706</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>44644</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45701</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45700</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>45085</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45743</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45706</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45743</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44970</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45772</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45196</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45509</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>45054</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45055</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45197</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45075</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>45246</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45722</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>45722</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>45210</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44734</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45744</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45085</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45058</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45455</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45275</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45369</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>44935</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45336</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>44896</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45344</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44985</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>44827</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>44543</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45743</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>44980</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>44595</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45281</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>44607</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44981</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45593</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45246</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44533</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45574</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45582</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45422</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45434</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45722</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45487</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45349</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>44967</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45086</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45075</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45727</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45672</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44649</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45366</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45638</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>45182</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33490,7 +33490,7 @@
         <v>45600</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>45600</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45708</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>45140</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45140</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>44711</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45261</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>44649</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>45177</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45197</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>45695</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34298,7 +34298,7 @@
         <v>45401</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34371,7 +34371,7 @@
         <v>45159</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34444,7 +34444,7 @@
         <v>45315</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>45279</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45328</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>45397</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45513</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45717</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45758</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45313</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>44851</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45272</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45401</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45259</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45238</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45642</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45720</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>45400</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>44622</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35690,7 +35690,7 @@
         <v>44620</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35763,7 +35763,7 @@
         <v>44657</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>44896</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>45222</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>44868</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>44895</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>45300</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44522</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45300</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>45425</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45428</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44895</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>45554</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>45355</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>45300</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45847</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>46042</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>46042</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>46042</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>46154</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>46154</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>46264</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
